--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -4574,6 +4574,21 @@
   </ns0:si>
   <ns0:si>
     <ns0:t>Firmament star</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>small DENG kitchen</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>小登厨</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>AoiGroove真琴</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>The Echo of Peach Color</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>蜜糖色的回响</ns0:t>
   </ns0:si>
 </ns0:sst>
 </file>
@@ -15337,6 +15352,28 @@
         <ns0:v>114</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="237" spans="1:16">
+      <ns0:c r="A237" s="12" t="s">
+        <ns0:v>1305</ns0:v>
+      </ns0:c>
+      <ns0:c r="B237" s="12" t="s">
+        <ns0:v>1306</ns0:v>
+      </ns0:c>
+      <ns0:c r="C237" s="12" t="s">
+        <ns0:v>1307</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="238" spans="1:16">
+      <ns0:c r="A238" s="12" t="s">
+        <ns0:v>1308</ns0:v>
+      </ns0:c>
+      <ns0:c r="B238" s="12" t="s">
+        <ns0:v>1309</ns0:v>
+      </ns0:c>
+      <ns0:c r="C238" s="12" t="s">
+        <ns0:v>1307</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:O233" ns1:filterBottomFollowUsedRange="0">
     <ns0:extLst/>

--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -4589,6 +4589,24 @@
   </ns0:si>
   <ns0:si>
     <ns0:t>蜜糖色的回响</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MIRROR</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MIRЯOЯ</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MIRBpmText</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>WHBpmText</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>花纪mirror南北绿豆（hanamicat x -200号）</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>?Owo!_WH</ns0:t>
   </ns0:si>
 </ns0:sst>
 </file>
@@ -15374,6 +15392,44 @@
         <ns0:v>1307</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="239" spans="1:16">
+      <ns0:c r="A239" s="12" t="s">
+        <ns0:v>1310</ns0:v>
+      </ns0:c>
+      <ns0:c r="B239" s="12" t="s">
+        <ns0:v>1311</ns0:v>
+      </ns0:c>
+      <ns0:c r="C239" s="12" t="s">
+        <ns0:v>1288</ns0:v>
+      </ns0:c>
+      <ns0:c r="H239" s="13">
+        <ns0:v>8.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="J239" s="13">
+        <ns0:v>11.4</ns0:v>
+      </ns0:c>
+      <ns0:c r="L239" s="13">
+        <ns0:v>12.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="G239" s="12" t="s">
+        <ns0:v>1312</ns0:v>
+      </ns0:c>
+      <ns0:c r="I239" s="12" t="s">
+        <ns0:v>1313</ns0:v>
+      </ns0:c>
+      <ns0:c r="K239" s="12" t="s">
+        <ns0:v>1314</ns0:v>
+      </ns0:c>
+      <ns0:c r="M239" s="12" t="s">
+        <ns0:v>89</ns0:v>
+      </ns0:c>
+      <ns0:c r="N239" s="12" t="s">
+        <ns0:v>1315</ns0:v>
+      </ns0:c>
+      <ns0:c r="O239" s="13">
+        <ns0:v>13.4</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:O233" ns1:filterBottomFollowUsedRange="0">
     <ns0:extLst/>
